--- a/outputs/purchase_intent_campaigns_20260716/01_ad_groups_staging_artifact.xlsx
+++ b/outputs/purchase_intent_campaigns_20260716/01_ad_groups_staging_artifact.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="Ra3d1fd0005834944"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet0" sheetId="1" r:id="Rb69e82f7877d4e75"/>
   </x:sheets>
 </x:workbook>
 </file>
